--- a/request_forms/008_food_culinary_referral_form--request_forms.xlsx
+++ b/request_forms/008_food_culinary_referral_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'program',_'value':_'program'}</t>
+          <t>program</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Program', 'value': 'Program'}</t>
+          <t>Program</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'service',_'value':_'service'}</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Service', 'value': 'Service'}</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'event',_'value':_'event'}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Event', 'value': 'Event'}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new',_'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'New', 'value': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new',_'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'New', 'value': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
